--- a/data/trans_orig/P57B1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido deprimido en 2023</t>
+          <t>Población según se ha sentido deprimido en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88359</t>
+          <t>92326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>83240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123448</t>
+          <t>126860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>134621</t>
+          <t>133860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201912</t>
+          <t>200328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>305639</t>
+          <t>300795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353100</t>
+          <t>352900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167191</t>
+          <t>167481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212278</t>
+          <t>212495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>483637</t>
+          <t>487997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>556595</t>
+          <t>556963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>92408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140744</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75187</t>
+          <t>72194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151261</t>
+          <t>149998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182604</t>
+          <t>185674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275662</t>
+          <t>274635</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>266342</t>
+          <t>265120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313172</t>
+          <t>314832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>330888</t>
+          <t>331463</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>419269</t>
+          <t>420416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>610708</t>
+          <t>613870</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>716579</t>
+          <t>716538</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35352</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>43184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>69029</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118185</t>
+          <t>115968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160198</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140821</t>
+          <t>141625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174838</t>
+          <t>173975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267568</t>
+          <t>267430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321546</t>
+          <t>322847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333757</t>
+          <t>333053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378440</t>
+          <t>378998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326938</t>
+          <t>327587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362260</t>
+          <t>362178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>670016</t>
+          <t>672579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729704</t>
+          <t>730650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64349</t>
+          <t>65283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104032</t>
+          <t>102684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85125</t>
+          <t>86917</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>277392</t>
+          <t>276174</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>205864</t>
+          <t>207347</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>270292</t>
+          <t>269155</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>250757</t>
+          <t>260276</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>530586</t>
+          <t>534302</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550697</t>
+          <t>551968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>781081</t>
+          <t>784189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369249</t>
+          <t>369489</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>455750</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>934403</t>
+          <t>927378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1286851</t>
+          <t>1273516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53280</t>
+          <t>51555</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>39761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66292</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>63058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>88511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120259</t>
+          <t>121610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>177335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217969</t>
+          <t>217961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191002</t>
+          <t>191298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>225220</t>
+          <t>224638</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>379238</t>
+          <t>381490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>434622</t>
+          <t>433492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>272109</t>
+          <t>271420</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>313882</t>
+          <t>313991</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>241629</t>
+          <t>243424</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>278790</t>
+          <t>278740</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526456</t>
+          <t>528168</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>583269</t>
+          <t>582300</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33065</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72542</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31472</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90335</t>
+          <t>91411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>116776</t>
+          <t>115983</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>146182</t>
+          <t>146023</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>218890</t>
+          <t>220199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>502653</t>
+          <t>503636</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>349407</t>
+          <t>347473</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>748407</t>
+          <t>728103</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>190562</t>
+          <t>188758</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>220169</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>80080</t>
+          <t>80848</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>297449</t>
+          <t>298523</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>187264</t>
+          <t>201129</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>511522</t>
+          <t>510666</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40633</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24794</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40191</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>53234</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74512</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>82414</t>
+          <t>80919</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>107497</t>
+          <t>107572</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>95118</t>
+          <t>93717</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>120695</t>
+          <t>120577</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>173337</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>202461</t>
+          <t>202939</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>275384</t>
+          <t>276031</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>313544</t>
+          <t>315153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>120752</t>
+          <t>121037</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>146493</t>
+          <t>147002</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>134118</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>161981</t>
+          <t>160626</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>263120</t>
+          <t>261336</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>302694</t>
+          <t>300995</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>88433</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>141203</t>
+          <t>140650</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>195298</t>
+          <t>190786</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>141458</t>
+          <t>137460</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>206825</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>226465</t>
+          <t>232016</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>311066</t>
+          <t>312613</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>400313</t>
+          <t>392413</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>505811</t>
+          <t>504889</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>743946</t>
+          <t>729565</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1034568</t>
+          <t>1037985</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1223061</t>
+          <t>1217813</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1793914</t>
+          <t>1736718</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2086998</t>
+          <t>2085068</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2860748</t>
+          <t>2779459</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2152979</t>
+          <t>2148417</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2523504</t>
+          <t>2526586</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1559751</t>
+          <t>1606274</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2039803</t>
+          <t>2042571</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3780572</t>
+          <t>3819303</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4441594</t>
+          <t>4456540</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61804</t>
+          <t>66415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>44291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>121480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83240</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126860</t>
+          <t>146339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>164574</t>
+          <t>187895</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>133860</t>
+          <t>155467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200328</t>
+          <t>227099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>332016</t>
+          <t>335137</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300795</t>
+          <t>310210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>352900</t>
+          <t>357379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>190931</t>
+          <t>219819</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167481</t>
+          <t>193269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212495</t>
+          <t>246012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>522947</t>
+          <t>554957</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>487997</t>
+          <t>515657</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>556963</t>
+          <t>589929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>56674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116202</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>115125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140335</t>
+          <t>168186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123043</t>
+          <t>141845</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72194</t>
+          <t>122737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149998</t>
+          <t>164925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>239246</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185674</t>
+          <t>249769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274635</t>
+          <t>312631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>289506</t>
+          <t>312378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265120</t>
+          <t>282743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314832</t>
+          <t>338461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>362873</t>
+          <t>330057</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>331463</t>
+          <t>305568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>420416</t>
+          <t>349269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>652379</t>
+          <t>642436</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>613870</t>
+          <t>607090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>716538</t>
+          <t>675770</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>510732</t>
+          <t>500274</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510732</t>
+          <t>500274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510732</t>
+          <t>500274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>934279</t>
+          <t>977164</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>934279</t>
+          <t>977164</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934279</t>
+          <t>977164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>43546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25152</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,67 +2011,67 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>36912</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>48098</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>64973</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>52308</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>79690</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>4,22%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>55608</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>43184</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>69029</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>136938</t>
+          <t>164467</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115968</t>
+          <t>141352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>187988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>157820</t>
+          <t>183953</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141625</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173975</t>
+          <t>203029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>294758</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267430</t>
+          <t>317557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322847</t>
+          <t>379066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>355935</t>
+          <t>407175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333053</t>
+          <t>381399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378998</t>
+          <t>431025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>345017</t>
+          <t>389370</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327587</t>
+          <t>368350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362178</t>
+          <t>409702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>700952</t>
+          <t>796545</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>672579</t>
+          <t>765570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730650</t>
+          <t>830240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>533933</t>
+          <t>618519</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>533933</t>
+          <t>618519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>533933</t>
+          <t>618519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541729</t>
+          <t>621393</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541729</t>
+          <t>621393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541729</t>
+          <t>621393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1075662</t>
+          <t>1239912</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1075662</t>
+          <t>1239912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1075662</t>
+          <t>1239912</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26092</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>48755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52201</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>46230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65283</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>79602</t>
+          <t>87272</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>71564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102684</t>
+          <t>105955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>191833</t>
+          <t>210441</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86917</t>
+          <t>184722</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>276174</t>
+          <t>234476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>245901</t>
+          <t>267689</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207347</t>
+          <t>246550</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>269155</t>
+          <t>287268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>437734</t>
+          <t>478130</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>260276</t>
+          <t>445780</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534302</t>
+          <t>512332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>652447</t>
+          <t>442598</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>551968</t>
+          <t>418876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>784189</t>
+          <t>468260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>394453</t>
+          <t>389813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369489</t>
+          <t>366571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439326</t>
+          <t>410665</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1046899</t>
+          <t>832411</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>927378</t>
+          <t>799480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1273516</t>
+          <t>870029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>886015</t>
+          <t>698930</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>886015</t>
+          <t>698930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>886015</t>
+          <t>698930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711044</t>
+          <t>734982</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711044</t>
+          <t>734982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711044</t>
+          <t>734982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1597058</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1597058</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1597058</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,22 +3071,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32668</t>
+          <t>35977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51555</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>55243</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65025</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>52355</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43031</t>
+          <t>46427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>113629</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88511</t>
+          <t>97737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121610</t>
+          <t>133651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>198245</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177335</t>
+          <t>192919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217961</t>
+          <t>238265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>207869</t>
+          <t>230408</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191298</t>
+          <t>213694</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>224638</t>
+          <t>248447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>406114</t>
+          <t>446718</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>381490</t>
+          <t>418254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>433492</t>
+          <t>475962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>292855</t>
+          <t>317743</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>271420</t>
+          <t>294194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>313991</t>
+          <t>342864</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>260905</t>
+          <t>289660</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>243424</t>
+          <t>270852</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>307829</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>553761</t>
+          <t>607403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>528168</t>
+          <t>577503</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>582300</t>
+          <t>636815</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>558872</t>
+          <t>606850</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>558872</t>
+          <t>606850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>558872</t>
+          <t>606850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>546629</t>
+          <t>607566</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>546629</t>
+          <t>607566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>546629</t>
+          <t>607566</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1105502</t>
+          <t>1214416</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105502</t>
+          <t>1214416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1105502</t>
+          <t>1214416</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45618</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72795</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>68424</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>62649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>91411</t>
+          <t>89678</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>130558</t>
+          <t>142287</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>115983</t>
+          <t>126033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>159188</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,67 +3831,67 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>354670</t>
+          <t>163756</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>220199</t>
+          <t>149959</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>503636</t>
+          <t>180628</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>34,24%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>306042</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>285148</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>327839</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>36,26%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>82,94%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>485228</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>347473</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>728103</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>49,79%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>205348</t>
+          <t>229537</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>188758</t>
+          <t>211968</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>220169</t>
+          <t>247132</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,67 +3944,67 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>192970</t>
+          <t>207792</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>80848</t>
+          <t>191662</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>298523</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>50,63%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>437328</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>414992</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>461567</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>51,81%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>49,16%</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>398317</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>201129</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>510666</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437945</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437945</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437945</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>974564</t>
+          <t>844136</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>974564</t>
+          <t>844136</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>974564</t>
+          <t>844136</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>34643</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40435</t>
+          <t>45715</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>45559</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>70050</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74351</t>
+          <t>81185</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>94426</t>
+          <t>105414</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>80919</t>
+          <t>91144</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>107572</t>
+          <t>119600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>107521</t>
+          <t>117887</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>93717</t>
+          <t>104394</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>120577</t>
+          <t>131555</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>187515</t>
+          <t>204011</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>173796</t>
+          <t>187454</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>202939</t>
+          <t>218866</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>295035</t>
+          <t>321898</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>276031</t>
+          <t>301145</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>315153</t>
+          <t>342553</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>133726</t>
+          <t>145934</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>121037</t>
+          <t>131746</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>147002</t>
+          <t>160177</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>147786</t>
+          <t>159748</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>133590</t>
+          <t>145638</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>160626</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>281512</t>
+          <t>305681</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>261336</t>
+          <t>285094</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>300995</t>
+          <t>327732</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>281349</t>
+          <t>308621</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>281349</t>
+          <t>308621</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>281349</t>
+          <t>308621</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>421315</t>
+          <t>459787</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>421315</t>
+          <t>459787</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>421315</t>
+          <t>459787</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>702663</t>
+          <t>768408</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>702663</t>
+          <t>768408</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>702663</t>
+          <t>768408</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>118046</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>167395</t>
+          <t>190317</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>140650</t>
+          <t>166970</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>190786</t>
+          <t>216207</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>177339</t>
+          <t>199246</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>175465</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>206484</t>
+          <t>227486</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>278726</t>
+          <t>311448</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>232016</t>
+          <t>283509</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>312613</t>
+          <t>341646</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>456065</t>
+          <t>510694</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>392413</t>
+          <t>474432</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>504889</t>
+          <t>553907</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>943101</t>
+          <t>1057340</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>729565</t>
+          <t>1000549</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1037985</t>
+          <t>1119213</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1379587</t>
+          <t>1313142</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1217813</t>
+          <t>1266341</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1736718</t>
+          <t>1371876</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,17 +5004,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2322688</t>
+          <t>2370482</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2085068</t>
+          <t>2291310</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2779459</t>
+          <t>2453396</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2261832</t>
+          <t>2190502</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2148417</t>
+          <t>2126657</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2526586</t>
+          <t>2252364</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1894936</t>
+          <t>1986260</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1606274</t>
+          <t>1933503</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2042571</t>
+          <t>2038487</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4156768</t>
+          <t>4176762</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3819303</t>
+          <t>4089823</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4456540</t>
+          <t>4256625</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
